--- a/ActivityTimeline.xlsx
+++ b/ActivityTimeline.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71227177-FAB5-4EFB-A2D1-33B846225B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631669C4-4145-47F3-909B-EFBDACFDC43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{0AFF59DF-243D-4E40-80BA-B8EFCDA293F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Activity 11</t>
+  </si>
+  <si>
+    <t>Chart Title</t>
   </si>
 </sst>
 </file>
@@ -148,18 +151,18 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -196,33 +199,15 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="2400" b="1">
-                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>Timeline</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Sheet1!$B$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>Chart Title</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:layout>
         <c:manualLayout>
@@ -270,7 +255,7 @@
           <c:yMode val="edge"/>
           <c:x val="2.6434576042103971E-2"/>
           <c:y val="5.2442559208200776E-2"/>
-          <c:w val="0.85182781606135394"/>
+          <c:w val="0.94886284497456685"/>
           <c:h val="0.93200424178154828"/>
         </c:manualLayout>
       </c:layout>
@@ -282,7 +267,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$2</c:f>
+              <c:f>Sheet1!$D$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -303,7 +288,10 @@
             <c:size val="10"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="0070C0"/>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="9525">
                 <a:noFill/>
@@ -317,7 +305,12 @@
               <c:symbol val="circle"/>
               <c:size val="10"/>
               <c:spPr>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
                 <a:ln w="9525">
                   <a:noFill/>
                 </a:ln>
@@ -377,7 +370,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -420,7 +412,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -463,7 +454,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -506,7 +496,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -549,7 +538,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -592,7 +580,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -635,7 +622,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -678,7 +664,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -721,7 +706,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -764,7 +748,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -807,7 +790,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -906,7 +888,7 @@
           </c:errBars>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$15</c:f>
+              <c:f>Sheet1!$B$5:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
                 <c:ptCount val="13"/>
@@ -947,14 +929,14 @@
                   <c:v>46188</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46266</c:v>
+                  <c:v>46235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$15</c:f>
+              <c:f>Sheet1!$D$5:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1004,7 +986,7 @@
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:datalabelsRange>
-                <c15:f>Sheet1!$C$3:$C$15</c15:f>
+                <c15:f>Sheet1!$C$5:$C$17</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="13"/>
                   <c:pt idx="0">
@@ -1733,13 +1715,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>600074</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1765,69 +1747,19 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB68EB80-90A2-AED3-8CF9-E62E9931FAA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="14458951" y="123825"/>
-          <a:ext cx="0" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E1E8998F-B012-4C27-AC7E-886717401112}" name="Activities" displayName="Activities" ref="B2:E15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="B2:E15" xr:uid="{E1E8998F-B012-4C27-AC7E-886717401112}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E1E8998F-B012-4C27-AC7E-886717401112}" name="Activities" displayName="Activities" ref="B4:E17" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="B4:E17" xr:uid="{E1E8998F-B012-4C27-AC7E-886717401112}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1F30CECC-201C-4D5E-97C9-76C78B78202B}" name="Date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{1F30CECC-201C-4D5E-97C9-76C78B78202B}" name="Date" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{7D5B744E-0E10-4550-9D65-7BD7F4A859C3}" name="Activity" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{B6CDD1BA-94F4-46E9-A404-7CEC34C129B6}" name="auto_level" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{B6CDD1BA-94F4-46E9-A404-7CEC34C129B6}" name="auto_level" dataDxfId="1">
       <calculatedColumnFormula>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{88C16322-6D27-4155-9B7F-A34A9A8740A8}" name="Level" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{88C16322-6D27-4155-9B7F-A34A9A8740A8}" name="Level" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2150,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{902A5A6D-E65C-4AF1-9971-C720D06D54D1}">
-  <dimension ref="B2:E15"/>
+  <dimension ref="B2:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -2159,64 +2091,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6">
-        <v>46023</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="3"/>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="6">
-        <v>46032</v>
+      <c r="B4" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2">
-        <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
-        <v>-5</v>
-      </c>
-      <c r="E4" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
-        <v>46042</v>
+        <v>46023</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
-        <v>46059</v>
+        <v>46032</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2226,10 +2137,10 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
-        <v>46068</v>
+        <v>46042</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2239,10 +2150,10 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="6">
-        <v>46088</v>
+        <v>46059</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2252,10 +2163,10 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="6">
-        <v>46122</v>
+        <v>46068</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2265,10 +2176,10 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="6">
-        <v>46127</v>
+        <v>46088</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2278,10 +2189,10 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="6">
-        <v>46160</v>
+        <v>46122</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2291,10 +2202,10 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="6">
-        <v>46167</v>
+        <v>46127</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2304,10 +2215,10 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2317,10 +2228,10 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
@@ -2330,16 +2241,42 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="6">
-        <v>46266</v>
+        <v>46174</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2">
         <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
+        <v>5</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="6">
+        <v>46188</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2">
+        <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
+        <v>-5</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="6">
+        <v>46235</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <f>IF(OR(Activities[[#This Row],[Activity]]="START_DATE",Activities[[#This Row],[Activity]]="END_DATE"),0,IF(Activities[[#This Row],[Level]]&lt;&gt;"",Activities[[#This Row],[Level]],CHOOSE(MOD(ROW()-ROW(Activities[[#Headers],[auto_level]])-1,2)+1,5,-5,10,-10)))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
